--- a/event_planner_forms/007_which_pumpkin_is_your_favorite_form--event_planner_forms.xlsx
+++ b/event_planner_forms/007_which_pumpkin_is_your_favorite_form--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -788,8 +788,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -817,12 +817,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'pumpkins',_'label':_'pumpkins',_'selected':_true}</t>
+          <t>pumpkins</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'pumpkins', 'label': 'Pumpkins', 'selected': True}</t>
+          <t>Pumpkins</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'gourds',_'label':_'gourds',_'selected':_false}</t>
+          <t>gourds</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'gourds', 'label': 'Gourds', 'selected': False}</t>
+          <t>Gourds</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'squash',_'label':_'squash',_'selected':_false}</t>
+          <t>squash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'squash', 'label': 'Squash', 'selected': False}</t>
+          <t>Squash</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other',_'label':_'other',_'selected':_false}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'other', 'label': 'Other', 'selected': False}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'green',_'label':_'green',_'selected':_false}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'green', 'label': 'Green', 'selected': False}</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'yellow',_'label':_'yellow',_'selected':_false}</t>
+          <t>yellow</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'yellow', 'label': 'Yellow', 'selected': False}</t>
+          <t>Yellow</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'orange',_'label':_'orange',_'selected':_false}</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'orange', 'label': 'Orange', 'selected': False}</t>
+          <t>Orange</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other',_'label':_'other',_'selected':_false}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'other', 'label': 'Other', 'selected': False}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'round',_'label':_'round',_'selected':_false}</t>
+          <t>round</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'round', 'label': 'Round', 'selected': False}</t>
+          <t>Round</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'square',_'label':_'square',_'selected':_false}</t>
+          <t>square</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'square', 'label': 'Square', 'selected': False}</t>
+          <t>Square</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'triangle',_'label':_'triangle',_'selected':_false}</t>
+          <t>triangle</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'triangle', 'label': 'Triangle', 'selected': False}</t>
+          <t>Triangle</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other',_'label':_'other',_'selected':_false}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'other', 'label': 'Other', 'selected': False}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
